--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5197,48 +5197,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104000083</v>
+        <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93201</v>
+        <v>93411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544581</v>
+        <v>544615</v>
       </c>
       <c r="R42" t="n">
-        <v>6961508</v>
+        <v>6961677</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5262,22 +5262,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5288,40 +5288,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000083</t>
+          <t>https://artportalen.se/Sighting/136859086</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104000084</v>
+        <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,37 +5320,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544702</v>
+        <v>544650</v>
       </c>
       <c r="R43" t="n">
-        <v>6961453</v>
+        <v>6961694</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5383,22 +5374,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5409,40 +5400,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000084</t>
+          <t>https://artportalen.se/Sighting/136859094</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104000094</v>
+        <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,37 +5432,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544688</v>
+        <v>544664</v>
       </c>
       <c r="R44" t="n">
-        <v>6961563</v>
+        <v>6961687</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5504,22 +5486,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5530,75 +5512,66 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000094</t>
+          <t>https://artportalen.se/Sighting/136859095</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104000165</v>
+        <v>104000083</v>
       </c>
       <c r="B45" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544638</v>
+        <v>544581</v>
       </c>
       <c r="R45" t="n">
-        <v>6961149</v>
+        <v>6961508</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5630,7 +5603,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5640,7 +5613,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5675,13 +5648,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000165</t>
+          <t>https://artportalen.se/Sighting/104000083</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119625383</v>
+        <v>104000084</v>
       </c>
       <c r="B46" t="n">
         <v>93209</v>
@@ -5712,17 +5685,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544594</v>
+        <v>544702</v>
       </c>
       <c r="R46" t="n">
-        <v>6961545</v>
+        <v>6961453</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5746,12 +5719,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5762,28 +5745,37 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625383</t>
+          <t>https://artportalen.se/Sighting/104000084</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119625390</v>
+        <v>104000094</v>
       </c>
       <c r="B47" t="n">
         <v>93209</v>
@@ -5814,17 +5806,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544640</v>
+        <v>544688</v>
       </c>
       <c r="R47" t="n">
-        <v>6961471</v>
+        <v>6961563</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5848,12 +5840,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,31 +5866,40 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625390</t>
+          <t>https://artportalen.se/Sighting/104000094</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119625384</v>
+        <v>104000165</v>
       </c>
       <c r="B48" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,37 +5907,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544582</v>
+        <v>544638</v>
       </c>
       <c r="R48" t="n">
-        <v>6961543</v>
+        <v>6961149</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5950,12 +5961,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5966,69 +5987,78 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625384</t>
+          <t>https://artportalen.se/Sighting/104000165</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104000122</v>
+        <v>119625383</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544854</v>
+        <v>544594</v>
       </c>
       <c r="R49" t="n">
-        <v>6961114</v>
+        <v>6961545</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6052,22 +6082,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6078,83 +6098,69 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000122</t>
+          <t>https://artportalen.se/Sighting/119625383</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104000171</v>
+        <v>119625390</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544671</v>
+        <v>544640</v>
       </c>
       <c r="R50" t="n">
-        <v>6961513</v>
+        <v>6961471</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6178,22 +6184,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,78 +6200,73 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000171</t>
+          <t>https://artportalen.se/Sighting/119625390</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119625388</v>
+        <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>93423</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544609</v>
+        <v>544720</v>
       </c>
       <c r="R51" t="n">
-        <v>6961486</v>
+        <v>6961673</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6299,12 +6290,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6319,27 +6320,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625388</t>
+          <t>https://artportalen.se/Sighting/136859096</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104000159</v>
+        <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>78730</v>
+        <v>93423</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6347,37 +6348,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544576</v>
+        <v>544690</v>
       </c>
       <c r="R52" t="n">
-        <v>6961517</v>
+        <v>6961555</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6401,22 +6402,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6427,40 +6428,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000159</t>
+          <t>https://artportalen.se/Sighting/136859119</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119625387</v>
+        <v>119625384</v>
       </c>
       <c r="B53" t="n">
-        <v>78730</v>
+        <v>93215</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6468,21 +6460,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>4368</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6492,10 +6484,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544571</v>
+        <v>544582</v>
       </c>
       <c r="R53" t="n">
-        <v>6961517</v>
+        <v>6961543</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6553,38 +6545,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625387</t>
+          <t>https://artportalen.se/Sighting/119625384</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104000170</v>
+        <v>104000122</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6594,10 +6586,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544816</v>
+        <v>544854</v>
       </c>
       <c r="R54" t="n">
-        <v>6961283</v>
+        <v>6961114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6621,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6631,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6650,6 +6642,11 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
@@ -6674,38 +6671,38 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000170</t>
+          <t>https://artportalen.se/Sighting/104000122</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104000139</v>
+        <v>104000171</v>
       </c>
       <c r="B55" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,10 +6712,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544676</v>
+        <v>544671</v>
       </c>
       <c r="R55" t="n">
-        <v>6961506</v>
+        <v>6961513</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6795,54 +6792,54 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000139</t>
+          <t>https://artportalen.se/Sighting/104000171</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104000078</v>
+        <v>119625388</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544893</v>
+        <v>544609</v>
       </c>
       <c r="R56" t="n">
-        <v>6961304</v>
+        <v>6961486</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6866,22 +6863,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6892,40 +6879,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000078</t>
+          <t>https://artportalen.se/Sighting/119625388</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128369903</v>
+        <v>104000159</v>
       </c>
       <c r="B57" t="n">
-        <v>97358</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6933,41 +6911,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>545259</v>
+        <v>544576</v>
       </c>
       <c r="R57" t="n">
-        <v>6960474</v>
+        <v>6961517</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6991,12 +6965,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7007,31 +6991,40 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369903</t>
+          <t>https://artportalen.se/Sighting/104000159</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104000103</v>
+        <v>119625387</v>
       </c>
       <c r="B58" t="n">
-        <v>78993</v>
+        <v>78730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7039,37 +7032,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544954</v>
+        <v>544571</v>
       </c>
       <c r="R58" t="n">
-        <v>6961093</v>
+        <v>6961517</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7093,22 +7086,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7119,40 +7102,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000103</t>
+          <t>https://artportalen.se/Sighting/119625387</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104000128</v>
+        <v>104000170</v>
       </c>
       <c r="B59" t="n">
-        <v>92208</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7160,21 +7134,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7158,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544971</v>
+        <v>544816</v>
       </c>
       <c r="R59" t="n">
-        <v>6961065</v>
+        <v>6961283</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7219,7 +7193,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7229,7 +7203,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7264,38 +7238,38 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000128</t>
+          <t>https://artportalen.se/Sighting/104000170</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104000047</v>
+        <v>104000139</v>
       </c>
       <c r="B60" t="n">
-        <v>90659</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1593</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7305,10 +7279,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544944</v>
+        <v>544676</v>
       </c>
       <c r="R60" t="n">
-        <v>6960924</v>
+        <v>6961506</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7340,7 +7314,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7350,7 +7324,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7385,54 +7359,54 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000047</t>
+          <t>https://artportalen.se/Sighting/104000139</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119625584</v>
+        <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>90674</v>
+        <v>98221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1596</v>
+        <v>221941</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>545189</v>
+        <v>544677</v>
       </c>
       <c r="R61" t="n">
-        <v>6961120</v>
+        <v>6961587</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7456,12 +7430,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7476,65 +7460,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625584</t>
+          <t>https://artportalen.se/Sighting/136859120</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119625583</v>
+        <v>104000078</v>
       </c>
       <c r="B62" t="n">
-        <v>93213</v>
+        <v>79085</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>545192</v>
+        <v>544893</v>
       </c>
       <c r="R62" t="n">
-        <v>6961119</v>
+        <v>6961304</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7558,12 +7542,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7574,69 +7568,82 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625583</t>
+          <t>https://artportalen.se/Sighting/104000078</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119625589</v>
+        <v>128369903</v>
       </c>
       <c r="B63" t="n">
-        <v>93213</v>
+        <v>97358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>545169</v>
+        <v>545259</v>
       </c>
       <c r="R63" t="n">
-        <v>6961145</v>
+        <v>6960474</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7660,12 +7667,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7680,65 +7687,65 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625589</t>
+          <t>https://artportalen.se/Sighting/128369903</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119625597</v>
+        <v>104000103</v>
       </c>
       <c r="B64" t="n">
-        <v>93213</v>
+        <v>78993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>545109</v>
+        <v>544954</v>
       </c>
       <c r="R64" t="n">
-        <v>6961124</v>
+        <v>6961093</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7762,12 +7769,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7778,31 +7795,40 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625597</t>
+          <t>https://artportalen.se/Sighting/104000103</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119625593</v>
+        <v>104000128</v>
       </c>
       <c r="B65" t="n">
-        <v>93222</v>
+        <v>92208</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,37 +7836,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3100</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>545146</v>
+        <v>544971</v>
       </c>
       <c r="R65" t="n">
-        <v>6961121</v>
+        <v>6961065</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7864,12 +7890,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7880,66 +7916,75 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625593</t>
+          <t>https://artportalen.se/Sighting/104000128</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>104000042</v>
+        <v>104000047</v>
       </c>
       <c r="B66" t="n">
-        <v>93189</v>
+        <v>90659</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>1593</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>545090</v>
+        <v>544944</v>
       </c>
       <c r="R66" t="n">
-        <v>6960936</v>
+        <v>6960924</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7971,7 +8016,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7981,7 +8026,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8016,38 +8061,38 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000042</t>
+          <t>https://artportalen.se/Sighting/104000047</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119625581</v>
+        <v>119625584</v>
       </c>
       <c r="B67" t="n">
-        <v>93189</v>
+        <v>90674</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8057,10 +8102,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>545208</v>
+        <v>545189</v>
       </c>
       <c r="R67" t="n">
-        <v>6961020</v>
+        <v>6961120</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8118,38 +8163,38 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625581</t>
+          <t>https://artportalen.se/Sighting/119625584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119625592</v>
+        <v>119625583</v>
       </c>
       <c r="B68" t="n">
-        <v>93189</v>
+        <v>93213</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8159,10 +8204,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>545146</v>
+        <v>545192</v>
       </c>
       <c r="R68" t="n">
-        <v>6961121</v>
+        <v>6961119</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8220,54 +8265,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625592</t>
+          <t>https://artportalen.se/Sighting/119625583</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104000050</v>
+        <v>119625589</v>
       </c>
       <c r="B69" t="n">
-        <v>93191</v>
+        <v>93213</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>545195</v>
+        <v>545169</v>
       </c>
       <c r="R69" t="n">
-        <v>6960820</v>
+        <v>6961145</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8291,22 +8336,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8317,78 +8352,69 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000050</t>
+          <t>https://artportalen.se/Sighting/119625589</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>104000076</v>
+        <v>119625597</v>
       </c>
       <c r="B70" t="n">
-        <v>93191</v>
+        <v>93213</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>545010</v>
+        <v>545109</v>
       </c>
       <c r="R70" t="n">
-        <v>6961039</v>
+        <v>6961124</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8412,22 +8438,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8438,40 +8454,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000076</t>
+          <t>https://artportalen.se/Sighting/119625597</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>104000092</v>
+        <v>119625593</v>
       </c>
       <c r="B71" t="n">
-        <v>93191</v>
+        <v>93222</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8479,37 +8486,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544973</v>
+        <v>545146</v>
       </c>
       <c r="R71" t="n">
-        <v>6960989</v>
+        <v>6961121</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8533,22 +8540,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>17:11</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>17:11</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8559,40 +8556,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000092</t>
+          <t>https://artportalen.se/Sighting/119625593</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>104000099</v>
+        <v>104000042</v>
       </c>
       <c r="B72" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8600,21 +8588,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8624,10 +8612,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>545246</v>
+        <v>545090</v>
       </c>
       <c r="R72" t="n">
-        <v>6960730</v>
+        <v>6960936</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8659,7 +8647,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8669,7 +8657,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8704,16 +8692,16 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000099</t>
+          <t>https://artportalen.se/Sighting/104000042</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>104000106</v>
+        <v>119625581</v>
       </c>
       <c r="B73" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8721,37 +8709,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>545005</v>
+        <v>545208</v>
       </c>
       <c r="R73" t="n">
-        <v>6961037</v>
+        <v>6961020</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8775,22 +8763,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8801,40 +8779,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000106</t>
+          <t>https://artportalen.se/Sighting/119625581</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>104000113</v>
+        <v>119625592</v>
       </c>
       <c r="B74" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8842,37 +8811,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544932</v>
+        <v>545146</v>
       </c>
       <c r="R74" t="n">
-        <v>6960572</v>
+        <v>6961121</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8896,22 +8865,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8922,37 +8881,28 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000113</t>
+          <t>https://artportalen.se/Sighting/119625592</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>104000162</v>
+        <v>104000050</v>
       </c>
       <c r="B75" t="n">
         <v>93191</v>
@@ -8987,10 +8937,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>545200</v>
+        <v>545195</v>
       </c>
       <c r="R75" t="n">
-        <v>6960831</v>
+        <v>6960820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9022,7 +8972,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9032,7 +8982,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9067,13 +9017,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000162</t>
+          <t>https://artportalen.se/Sighting/104000050</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119625574</v>
+        <v>104000076</v>
       </c>
       <c r="B76" t="n">
         <v>93191</v>
@@ -9104,17 +9054,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544964</v>
+        <v>545010</v>
       </c>
       <c r="R76" t="n">
-        <v>6960939</v>
+        <v>6961039</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9138,12 +9088,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9154,28 +9114,37 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625574</t>
+          <t>https://artportalen.se/Sighting/104000076</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625576</v>
+        <v>104000092</v>
       </c>
       <c r="B77" t="n">
         <v>93191</v>
@@ -9206,17 +9175,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>545048</v>
+        <v>544973</v>
       </c>
       <c r="R77" t="n">
-        <v>6960895</v>
+        <v>6960989</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9240,12 +9209,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9256,28 +9235,37 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625576</t>
+          <t>https://artportalen.se/Sighting/104000092</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625578</v>
+        <v>104000099</v>
       </c>
       <c r="B78" t="n">
         <v>93191</v>
@@ -9308,17 +9296,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>545085</v>
+        <v>545246</v>
       </c>
       <c r="R78" t="n">
-        <v>6960933</v>
+        <v>6960730</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9342,12 +9330,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9358,28 +9356,37 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625578</t>
+          <t>https://artportalen.se/Sighting/104000099</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625579</v>
+        <v>104000106</v>
       </c>
       <c r="B79" t="n">
         <v>93191</v>
@@ -9410,17 +9417,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>545270</v>
+        <v>545005</v>
       </c>
       <c r="R79" t="n">
-        <v>6960997</v>
+        <v>6961037</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9444,12 +9451,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9460,28 +9477,37 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625579</t>
+          <t>https://artportalen.se/Sighting/104000106</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119625580</v>
+        <v>104000113</v>
       </c>
       <c r="B80" t="n">
         <v>93191</v>
@@ -9512,17 +9538,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>545279</v>
+        <v>544932</v>
       </c>
       <c r="R80" t="n">
-        <v>6961027</v>
+        <v>6960572</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9546,12 +9572,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9562,28 +9598,37 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625580</t>
+          <t>https://artportalen.se/Sighting/104000113</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119625582</v>
+        <v>104000162</v>
       </c>
       <c r="B81" t="n">
         <v>93191</v>
@@ -9614,17 +9659,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>545184</v>
+        <v>545200</v>
       </c>
       <c r="R81" t="n">
-        <v>6961041</v>
+        <v>6960831</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9648,12 +9693,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9664,28 +9719,37 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625582</t>
+          <t>https://artportalen.se/Sighting/104000162</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119625585</v>
+        <v>119625574</v>
       </c>
       <c r="B82" t="n">
         <v>93191</v>
@@ -9720,10 +9784,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>545189</v>
+        <v>544964</v>
       </c>
       <c r="R82" t="n">
-        <v>6961131</v>
+        <v>6960939</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9781,13 +9845,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625585</t>
+          <t>https://artportalen.se/Sighting/119625574</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119625591</v>
+        <v>119625576</v>
       </c>
       <c r="B83" t="n">
         <v>93191</v>
@@ -9822,10 +9886,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>545162</v>
+        <v>545048</v>
       </c>
       <c r="R83" t="n">
-        <v>6961129</v>
+        <v>6960895</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9866,7 +9930,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9884,13 +9947,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625591</t>
+          <t>https://artportalen.se/Sighting/119625576</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625594</v>
+        <v>119625578</v>
       </c>
       <c r="B84" t="n">
         <v>93191</v>
@@ -9925,10 +9988,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>545146</v>
+        <v>545085</v>
       </c>
       <c r="R84" t="n">
-        <v>6961121</v>
+        <v>6960933</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9986,13 +10049,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625594</t>
+          <t>https://artportalen.se/Sighting/119625578</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119625596</v>
+        <v>119625579</v>
       </c>
       <c r="B85" t="n">
         <v>93191</v>
@@ -10027,10 +10090,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>545102</v>
+        <v>545270</v>
       </c>
       <c r="R85" t="n">
-        <v>6961133</v>
+        <v>6960997</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10088,13 +10151,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625596</t>
+          <t>https://artportalen.se/Sighting/119625579</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119625598</v>
+        <v>119625580</v>
       </c>
       <c r="B86" t="n">
         <v>93191</v>
@@ -10129,10 +10192,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>545110</v>
+        <v>545279</v>
       </c>
       <c r="R86" t="n">
-        <v>6961114</v>
+        <v>6961027</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10190,13 +10253,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625598</t>
+          <t>https://artportalen.se/Sighting/119625580</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119625599</v>
+        <v>119625582</v>
       </c>
       <c r="B87" t="n">
         <v>93191</v>
@@ -10231,10 +10294,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>545111</v>
+        <v>545184</v>
       </c>
       <c r="R87" t="n">
-        <v>6961107</v>
+        <v>6961041</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10292,16 +10355,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625599</t>
+          <t>https://artportalen.se/Sighting/119625582</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119625606</v>
+        <v>119625585</v>
       </c>
       <c r="B88" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10309,21 +10372,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10333,10 +10396,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544967</v>
+        <v>545189</v>
       </c>
       <c r="R88" t="n">
-        <v>6961196</v>
+        <v>6961131</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10377,7 +10440,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10395,54 +10457,54 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625606</t>
+          <t>https://artportalen.se/Sighting/119625585</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104000098</v>
+        <v>119625591</v>
       </c>
       <c r="B89" t="n">
-        <v>92869</v>
+        <v>93191</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4769</v>
+        <v>4362</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>545437</v>
+        <v>545162</v>
       </c>
       <c r="R89" t="n">
-        <v>6960643</v>
+        <v>6961129</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10466,22 +10528,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10490,80 +10542,72 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000098</t>
+          <t>https://artportalen.se/Sighting/119625591</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>104000173</v>
+        <v>119625594</v>
       </c>
       <c r="B90" t="n">
-        <v>92869</v>
+        <v>93191</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4769</v>
+        <v>4362</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>545111</v>
+        <v>545146</v>
       </c>
       <c r="R90" t="n">
-        <v>6960891</v>
+        <v>6961121</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10587,22 +10631,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10613,62 +10647,53 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000173</t>
+          <t>https://artportalen.se/Sighting/119625594</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119625575</v>
+        <v>119625596</v>
       </c>
       <c r="B91" t="n">
-        <v>90691</v>
+        <v>93191</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10678,10 +10703,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>545016</v>
+        <v>545102</v>
       </c>
       <c r="R91" t="n">
-        <v>6960898</v>
+        <v>6961133</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10739,38 +10764,38 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625575</t>
+          <t>https://artportalen.se/Sighting/119625596</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119625588</v>
+        <v>119625598</v>
       </c>
       <c r="B92" t="n">
-        <v>90691</v>
+        <v>93191</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10780,10 +10805,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>545183</v>
+        <v>545110</v>
       </c>
       <c r="R92" t="n">
-        <v>6961139</v>
+        <v>6961114</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10841,16 +10866,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625588</t>
+          <t>https://artportalen.se/Sighting/119625598</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>104000079</v>
+        <v>119625599</v>
       </c>
       <c r="B93" t="n">
-        <v>83307</v>
+        <v>93191</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10858,37 +10883,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>4362</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>545426</v>
+        <v>545111</v>
       </c>
       <c r="R93" t="n">
-        <v>6960672</v>
+        <v>6961107</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10912,22 +10937,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10938,40 +10953,31 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000079</t>
+          <t>https://artportalen.se/Sighting/119625599</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>104000095</v>
+        <v>119625606</v>
       </c>
       <c r="B94" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10979,37 +10985,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>545033</v>
+        <v>544967</v>
       </c>
       <c r="R94" t="n">
-        <v>6961085</v>
+        <v>6961196</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11033,22 +11039,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11057,42 +11053,34 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000095</t>
+          <t>https://artportalen.se/Sighting/119625606</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119625601</v>
+        <v>104000098</v>
       </c>
       <c r="B95" t="n">
-        <v>57141</v>
+        <v>92869</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11100,41 +11088,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>545027</v>
+        <v>545437</v>
       </c>
       <c r="R95" t="n">
-        <v>6961112</v>
+        <v>6960643</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11158,12 +11142,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11174,71 +11168,75 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625601</t>
+          <t>https://artportalen.se/Sighting/104000098</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>104000132</v>
+        <v>104000173</v>
       </c>
       <c r="B96" t="n">
-        <v>5495</v>
+        <v>92869</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>101410</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>545000</v>
+        <v>545111</v>
       </c>
       <c r="R96" t="n">
-        <v>6960954</v>
+        <v>6960891</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11270,7 +11268,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11280,7 +11278,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11314,6 +11312,684 @@
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000173</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>119625575</v>
+      </c>
+      <c r="B97" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>545016</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6960898</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625575</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>119625588</v>
+      </c>
+      <c r="B98" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>545183</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6961139</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625588</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>104000079</v>
+      </c>
+      <c r="B99" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Storflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>545426</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6960672</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000079</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>104000095</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>545033</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6961085</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000095</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>119625601</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>545027</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6961112</v>
+      </c>
+      <c r="S101" t="n">
+        <v>25</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625601</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>104000132</v>
+      </c>
+      <c r="B102" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>545000</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6960954</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104000132</t>
         </is>
@@ -11416,6 +12092,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5200,7 +5200,7 @@
         <v>136859086</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136859094</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>136859095</v>
       </c>
       <c r="B44" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136859096</v>
       </c>
       <c r="B51" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>136859119</v>
       </c>
       <c r="B52" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>136859120</v>
       </c>
       <c r="B61" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
